--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.978804808250195</v>
+        <v>1.296555781340657</v>
       </c>
       <c r="D2" t="n">
-        <v>7.574855421627171</v>
+        <v>1.230914006014415</v>
       </c>
       <c r="E2" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F2" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.2969843420459</v>
+        <v>6.548259955582458</v>
       </c>
       <c r="D3" t="n">
-        <v>41.01569301254673</v>
+        <v>6.665050114538843</v>
       </c>
       <c r="E3" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F3" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.17271346347086</v>
+        <v>5.390565937814015</v>
       </c>
       <c r="D4" t="n">
-        <v>33.6822452053989</v>
+        <v>5.473364845877321</v>
       </c>
       <c r="E4" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F4" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.11115743133476</v>
+        <v>4.568063082591899</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49137441140332</v>
+        <v>4.62984834185304</v>
       </c>
       <c r="E5" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F5" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.68169638103396</v>
+        <v>6.935775661918019</v>
       </c>
       <c r="D6" t="n">
-        <v>43.0334619109349</v>
+        <v>6.992937560526922</v>
       </c>
       <c r="E6" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F6" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.48912159440641</v>
+        <v>9.179482259091042</v>
       </c>
       <c r="D7" t="n">
-        <v>56.48757538006219</v>
+        <v>9.179230999260106</v>
       </c>
       <c r="E7" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F7" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.58676731732025</v>
+        <v>3.995349689064541</v>
       </c>
       <c r="D8" t="n">
-        <v>24.244922938341</v>
+        <v>3.939799977480413</v>
       </c>
       <c r="E8" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F8" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.86228812250719</v>
+        <v>8.427621819907419</v>
       </c>
       <c r="D9" t="n">
-        <v>51.71572543753887</v>
+        <v>8.403805383600067</v>
       </c>
       <c r="E9" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F9" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.37188880381396</v>
+        <v>5.910431930619769</v>
       </c>
       <c r="D10" t="n">
-        <v>35.8496701126535</v>
+        <v>5.825571393306194</v>
       </c>
       <c r="E10" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F10" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.27079560590552</v>
+        <v>5.731504285959647</v>
       </c>
       <c r="D11" t="n">
-        <v>34.54372927299934</v>
+        <v>5.613356006862394</v>
       </c>
       <c r="E11" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F11" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.30244796092784</v>
+        <v>7.849147793650775</v>
       </c>
       <c r="D12" t="n">
-        <v>47.98760929882381</v>
+        <v>7.79798651105887</v>
       </c>
       <c r="E12" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F12" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.98127921730348</v>
+        <v>7.146957872811816</v>
       </c>
       <c r="D13" t="n">
-        <v>43.24330809422086</v>
+        <v>7.027037565310891</v>
       </c>
       <c r="E13" t="n">
-        <v>12.62120805564165</v>
+        <v>2.050946309041767</v>
       </c>
       <c r="F13" t="n">
-        <v>12.67082195033037</v>
+        <v>2.059008566928685</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
